--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>97329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132408519</v>
       </c>
       <c r="B3" t="n">
-        <v>89274</v>
+        <v>89277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>132408593</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132408438</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
+        <v>97329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97329</v>
+        <v>97337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132408519</v>
       </c>
       <c r="B3" t="n">
-        <v>89277</v>
+        <v>89283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>132408593</v>
       </c>
       <c r="B4" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132408438</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97329</v>
+        <v>97337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97337</v>
+        <v>97347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132408519</v>
       </c>
       <c r="B3" t="n">
-        <v>89283</v>
+        <v>89291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>132408593</v>
       </c>
       <c r="B4" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132408438</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97337</v>
+        <v>97347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97347</v>
+        <v>97348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132408519</v>
       </c>
       <c r="B3" t="n">
-        <v>89291</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>132408593</v>
       </c>
       <c r="B4" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97347</v>
+        <v>97348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97348</v>
+        <v>97349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97348</v>
+        <v>97349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97357</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97349</v>
+        <v>97350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132408519</v>
       </c>
       <c r="B3" t="n">
-        <v>89292</v>
+        <v>89293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>132408593</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132408438</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97349</v>
+        <v>97350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97350</v>
+        <v>97352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132408519</v>
       </c>
       <c r="B3" t="n">
-        <v>89293</v>
+        <v>89295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>132408593</v>
       </c>
       <c r="B4" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97350</v>
+        <v>97352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408452</v>
       </c>
       <c r="B2" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132408519</v>
       </c>
       <c r="B3" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>132408593</v>
       </c>
       <c r="B4" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>132408438</v>
       </c>
       <c r="B5" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>132408484</v>
       </c>
       <c r="B6" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>132408591</v>
       </c>
       <c r="B7" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132408452</v>
+        <v>132408591</v>
       </c>
       <c r="B2" t="n">
-        <v>97357</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yrmyrsmossen, Dls</t>
+          <t>Sydväst Laxetjärnsmossen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352338</v>
+        <v>352627</v>
       </c>
       <c r="R2" t="n">
-        <v>6556012</v>
+        <v>6555963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,24 +747,14 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På nordvänd, fuktig lodyta.</t>
+          <t>På granlåga i fuktig naturskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132408519</v>
+        <v>132408452</v>
       </c>
       <c r="B3" t="n">
-        <v>89299</v>
+        <v>97426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,21 +817,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Naturskog syd Yrmyrsmossen, Dls</t>
+          <t>Yrmyrsmossen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352447</v>
+        <v>352338</v>
       </c>
       <c r="R3" t="n">
-        <v>6556040</v>
+        <v>6556012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På klen granlåga i naturskog i nordsluttning</t>
+          <t>På nordvänd, fuktig lodyta.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,48 +907,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132408593</v>
+        <v>132408484</v>
       </c>
       <c r="B4" t="n">
-        <v>91880</v>
+        <v>97426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydväst Laxetjärnsmossen, Dls</t>
+          <t>Yrmyrsmossen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>352627</v>
+        <v>352369</v>
       </c>
       <c r="R4" t="n">
-        <v>6555963</v>
+        <v>6556043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,9 +979,24 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På nordvänd, fuktig lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132408438</v>
+        <v>132408519</v>
       </c>
       <c r="B5" t="n">
-        <v>79332</v>
+        <v>89354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,37 +1035,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yrmyrsmossen, Dls</t>
+          <t>Naturskog syd Yrmyrsmossen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>352337</v>
+        <v>352447</v>
       </c>
       <c r="R5" t="n">
-        <v>6556021</v>
+        <v>6556040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1120,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hängande på grankvist i myrkant</t>
+          <t>På klen granlåga i naturskog i nordsluttning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,49 +1148,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132408484</v>
+        <v>132408593</v>
       </c>
       <c r="B6" t="n">
-        <v>97357</v>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yrmyrsmossen, Dls</t>
+          <t>Sydväst Laxetjärnsmossen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>352369</v>
+        <v>352627</v>
       </c>
       <c r="R6" t="n">
-        <v>6556043</v>
+        <v>6555963</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,24 +1219,9 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På nordvänd, fuktig lodyta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,49 +1249,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132408591</v>
+        <v>132408438</v>
       </c>
       <c r="B7" t="n">
-        <v>97366</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst Laxetjärnsmossen, Dls</t>
+          <t>Yrmyrsmossen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>352627</v>
+        <v>352337</v>
       </c>
       <c r="R7" t="n">
-        <v>6555963</v>
+        <v>6556021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,14 +1320,24 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga i fuktig naturskog</t>
+          <t>Hängande på grankvist i myrkant</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13217-2026 artfynd.xlsx
+++ b/artfynd/A 13217-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132408591</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132408452</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132408484</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132408519</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132408593</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,8 +1392,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132408438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>